--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 01:02:47</t>
+          <t>2026-06-06 03:14:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 03:14:35</t>
+          <t>2026-06-06 05:26:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 05:26:12</t>
+          <t>2026-06-06 07:38:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 07:38:48</t>
+          <t>2026-06-06 09:51:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 09:51:35</t>
+          <t>2026-06-06 12:03:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,212 +875,212 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1129,212 +1129,212 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,515 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 12:03:22</t>
+          <t>2026-06-06 14:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-06 14:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-06 14:14:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="S2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.02</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
         <v>1.19</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
         <v>1.19</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1377,218 +1377,218 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -1631,218 +1631,218 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 14:14:44</t>
+          <t>2026-06-06 16:24:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1141,7 +1141,7 @@
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.19</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.12</v>
@@ -1407,16 +1407,16 @@
         <v>1.11</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.19</v>
@@ -1661,13 +1661,13 @@
         <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 16:24:59</t>
+          <t>2026-06-06 18:34:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -896,7 +896,7 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1135,16 +1135,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Junior FC Barranquill</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X6" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO6" t="n">
         <v>3.25</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2604,7 +2604,261 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 18:34:43</t>
+          <t>2026-06-06 20:44:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-06 20:44:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -896,7 +896,7 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.18</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1392,13 +1392,13 @@
         <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
         <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1643,19 +1643,19 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
         <v>1.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="G6" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
         <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -1933,34 +1933,34 @@
         <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
         <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
         <v>970</v>
@@ -1969,73 +1969,73 @@
         <v>970</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AO6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AV6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="BA6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH6" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4</v>
       </c>
       <c r="BI6" t="n">
         <v>3.1</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="BN6" t="n">
         <v>4.2</v>
@@ -2062,13 +2062,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.21</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2160,7 +2160,7 @@
         <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
@@ -2172,16 +2172,16 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
         <v>14</v>
@@ -2235,16 +2235,16 @@
         <v>130</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>9.800000000000001</v>
@@ -2268,7 +2268,7 @@
         <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>21</v>
@@ -2277,80 +2277,80 @@
         <v>21</v>
       </c>
       <c r="BD7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BH7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-06 20:44:19</t>
+          <t>2026-06-06 22:53:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BK Olympic</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.18</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Stockholm Internazionale</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>BK Olympic</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.18</v>
@@ -1150,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>FC Stockholm Internazionale</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Junior FC Barranquill</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>2.64</v>
+        <v>1.18</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>2.52</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,1514 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-06 22:53:29</t>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-07 01:02:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquill</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-07 01:02:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-07 01:02:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-07 01:02:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Atletico GO</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-06 22:53:29</t>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-07 01:02:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,157 +857,157 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>1.42</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
         <v>1.03</v>
@@ -1019,13 +1019,13 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,13 +1037,13 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
@@ -1055,7 +1055,7 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2127,157 +2127,157 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
         <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
         <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
         <v>1.03</v>
@@ -2289,10 +2289,10 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2307,7 +2307,7 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2381,157 +2381,157 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
         <v>1.03</v>
@@ -2546,7 +2546,7 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2635,172 +2635,172 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
         <v>1.66</v>
@@ -2898,46 +2898,46 @@
         <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
         <v>2.52</v>
@@ -2952,13 +2952,13 @@
         <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2994,19 +2994,19 @@
         <v>10</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
         <v>4.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -3015,10 +3015,10 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
         <v>7.6</v>
@@ -3027,34 +3027,34 @@
         <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.76</v>
+        <v>4.6</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3176,7 +3176,7 @@
         <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3212,7 +3212,7 @@
         <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>19.5</v>
@@ -3257,10 +3257,10 @@
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -3272,7 +3272,7 @@
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -3284,7 +3284,7 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -3296,13 +3296,13 @@
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3344,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 01:02:59</t>
+          <t>2026-06-07 03:12:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.85</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,206 +881,206 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.02</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.89</v>
-      </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK2" t="n">
         <v>29</v>
       </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BN2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU2" t="n">
         <v>4.6</v>
       </c>
-      <c r="BO2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT2" t="n">
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>8.4</v>
       </c>
-      <c r="BU2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
@@ -1144,7 +1144,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -1365,190 +1365,190 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.1</v>
       </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,29 +1566,29 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N5" t="n">
         <v>1.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1.12</v>
+        <v>1.89</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.09</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.2</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
         <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2193,34 +2193,34 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC7" t="n">
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
@@ -2235,122 +2235,122 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2453,7 +2453,7 @@
         <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2465,19 +2465,19 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK8" t="n">
         <v>22</v>
       </c>
-      <c r="AK8" t="n">
-        <v>25</v>
-      </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,122 +2489,122 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
         <v>3.75</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
         <v>11</v>
@@ -2698,7 +2698,7 @@
         <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
@@ -2710,7 +2710,7 @@
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>28</v>
@@ -2719,146 +2719,146 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AR9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BU9" t="n">
         <v>3.5</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -2889,34 +2889,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I10" t="n">
         <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
         <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
         <v>2.06</v>
@@ -2928,31 +2928,31 @@
         <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
         <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
         <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2970,7 +2970,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
@@ -2997,13 +2997,13 @@
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
         <v>5</v>
@@ -3012,13 +3012,13 @@
         <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
         <v>7.6</v>
@@ -3027,31 +3027,31 @@
         <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
         <v>4.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI10" t="n">
         <v>3</v>
@@ -3060,13 +3060,13 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.34</v>
+        <v>1.97</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.34</v>
+        <v>1.98</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>2.06</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -3149,25 +3149,25 @@
         <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
         <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1.43</v>
@@ -3194,7 +3194,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
@@ -3209,7 +3209,7 @@
         <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3257,10 +3257,10 @@
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -3272,7 +3272,7 @@
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -3284,7 +3284,7 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -3296,77 +3296,77 @@
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
         <v>3.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 03:12:27</t>
+          <t>2026-06-07 10:45:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -866,7 +866,7 @@
         <v>4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -881,7 +881,7 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
@@ -896,7 +896,7 @@
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
@@ -926,7 +926,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>27</v>
@@ -965,10 +965,10 @@
         <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -977,13 +977,13 @@
         <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AW2" t="n">
         <v>4.2</v>
@@ -992,19 +992,19 @@
         <v>3.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC2" t="n">
         <v>3.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
         <v>4.1</v>
@@ -1013,7 +1013,7 @@
         <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG2" t="n">
         <v>4.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="n">
         <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.22</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W4" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1425,7 +1425,7 @@
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1440,7 +1440,7 @@
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1449,19 +1449,19 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,79 +1470,79 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
@@ -1560,35 +1560,35 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
         <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
@@ -1646,37 +1646,37 @@
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="T5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
@@ -1685,7 +1685,7 @@
         <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1697,16 +1697,16 @@
         <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
         <v>26</v>
@@ -1715,134 +1715,134 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AW5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BD5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI5" t="n">
         <v>3.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.55</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO5" t="n">
         <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
         <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CA5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1873,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
@@ -1903,7 +1903,7 @@
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
         <v>1.2</v>
@@ -1924,61 +1924,61 @@
         <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G7" t="n">
         <v>1.79</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2172,7 +2172,7 @@
         <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
         <v>1.15</v>
@@ -2202,7 +2202,7 @@
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -2214,7 +2214,7 @@
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>970</v>
@@ -2235,10 +2235,10 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
         <v>5.9</v>
@@ -2247,7 +2247,7 @@
         <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
         <v>3.9</v>
@@ -2265,7 +2265,7 @@
         <v>4.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
         <v>6.2</v>
@@ -2280,7 +2280,7 @@
         <v>5.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.2</v>
+        <v>1.93</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
@@ -2414,13 +2414,13 @@
         <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
         <v>1.95</v>
@@ -2441,7 +2441,7 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2474,10 +2474,10 @@
         <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,64 +2489,64 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="AT8" t="n">
         <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AX8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BA8" t="n">
         <v>3.5</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BB8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG8" t="n">
         <v>3.55</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.85</v>
       </c>
       <c r="BH8" t="n">
         <v>6.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
         <v>3.75</v>
@@ -2677,10 +2677,10 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
         <v>1.58</v>
@@ -2800,7 +2800,7 @@
         <v>2.96</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2833,7 +2833,7 @@
         <v>1.7</v>
       </c>
       <c r="BT9" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BU9" t="n">
         <v>3.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.93</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3308,7 +3308,7 @@
         <v>3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.47</v>
@@ -3421,13 +3421,13 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
         <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
         <v>2.6</v>
@@ -3436,7 +3436,7 @@
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -3445,10 +3445,10 @@
         <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>9</v>
@@ -3568,13 +3568,13 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
         <v>4.8</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>8</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 10:45:44</t>
+          <t>2026-06-07 11:15:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,34 +881,34 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.02</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -920,13 +920,13 @@
         <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>27</v>
@@ -965,10 +965,10 @@
         <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -977,34 +977,34 @@
         <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.8</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
         <v>4.1</v>
@@ -1013,74 +1013,74 @@
         <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
         <v>4.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.32</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO2" t="n">
         <v>3.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -1111,196 +1111,196 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,29 +1312,29 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.24</v>
@@ -1389,22 +1389,22 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
         <v>1.57</v>
@@ -1413,10 +1413,10 @@
         <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1428,7 +1428,7 @@
         <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1440,7 +1440,7 @@
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1455,13 +1455,13 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,125 +1470,125 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.66</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.31</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.53</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.11</v>
+        <v>5.1</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
@@ -1643,40 +1643,40 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
@@ -1685,7 +1685,7 @@
         <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1697,7 +1697,7 @@
         <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1727,64 +1727,64 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW5" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AX5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.6</v>
       </c>
       <c r="BH5" t="n">
         <v>6.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
@@ -1802,7 +1802,7 @@
         <v>5.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
         <v>1.53</v>
@@ -1885,13 +1885,13 @@
         <v>1.69</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1900,43 +1900,43 @@
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AB6" t="n">
         <v>950</v>
@@ -1945,10 +1945,10 @@
         <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AF6" t="n">
         <v>65</v>
@@ -1981,122 +1981,122 @@
         <v>8.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>1.63</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -2145,40 +2145,40 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.06</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2187,16 +2187,16 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
@@ -2205,7 +2205,7 @@
         <v>150</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -2235,61 +2235,61 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
         <v>2.52</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>5</v>
       </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
         <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I8" t="n">
         <v>7.4</v>
@@ -2396,37 +2396,37 @@
         <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
         <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.95</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
@@ -2441,7 +2441,7 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2489,129 +2489,129 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="AR8" t="n">
         <v>3.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AW8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX8" t="n">
         <v>3.5</v>
       </c>
-      <c r="AX8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AY8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BA8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD8" t="n">
         <v>3.5</v>
       </c>
-      <c r="BB8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
         <v>3.7</v>
       </c>
-      <c r="BD8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.44</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>2.74</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.32</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
         <v>70</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>80</v>
-      </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4</v>
-      </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Junior FC Barranquill</t>
+          <t>CD Trasandino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>2.62</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA11" t="n">
         <v>4.5</v>
       </c>
-      <c r="I11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BT11" t="n">
         <v>15.5</v>
       </c>
-      <c r="BN11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO11" t="n">
+      <c r="BU11" t="n">
         <v>3.55</v>
       </c>
-      <c r="BP11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>1.64</v>
       </c>
       <c r="BZ11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>11</v>
+        <v>1.64</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W12" t="n">
         <v>2.66</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.84</v>
-      </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN12" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BO12" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:15:26</t>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,1260 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.64</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>11</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>25</v>
       </c>
-      <c r="AA13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL13" t="n">
         <v>48</v>
       </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>65</v>
-      </c>
       <c r="AM13" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
       </c>
       <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AS13" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="T14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>4.2</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BA14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP15" t="n">
         <v>23</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT13" t="n">
+      <c r="BQ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT15" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="BU15" t="n">
         <v>5</v>
       </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-07 11:15:26</t>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Union Espanola</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Union San Felipe</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-07 13:23:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -863,7 +863,7 @@
         <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>6.6</v>
@@ -896,7 +896,7 @@
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -905,7 +905,7 @@
         <v>1.77</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
         <v>2.04</v>
@@ -926,7 +926,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>27</v>
@@ -989,7 +989,7 @@
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
@@ -998,7 +998,7 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
         <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>29</v>
@@ -1177,10 +1177,10 @@
         <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1189,10 +1189,10 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>970</v>
@@ -1201,10 +1201,10 @@
         <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>36</v>
@@ -1216,125 +1216,125 @@
         <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.06</v>
+        <v>4.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.08</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>18</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.08</v>
+        <v>16.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.08</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
         <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1392,7 +1392,7 @@
         <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>2.48</v>
@@ -1404,16 +1404,16 @@
         <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
         <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>2.12</v>
@@ -1425,7 +1425,7 @@
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>110</v>
@@ -1494,7 +1494,7 @@
         <v>4.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
         <v>4.2</v>
@@ -1506,7 +1506,7 @@
         <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
         <v>4.5</v>
@@ -1521,7 +1521,7 @@
         <v>3.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
         <v>5</v>
@@ -1530,19 +1530,19 @@
         <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.17</v>
@@ -1649,28 +1649,28 @@
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>55</v>
@@ -1712,7 +1712,7 @@
         <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1727,7 +1727,7 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.2</v>
@@ -1745,16 +1745,16 @@
         <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW5" t="n">
         <v>5.3</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>11.5</v>
@@ -1763,7 +1763,7 @@
         <v>5.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1772,77 +1772,77 @@
         <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
         <v>4.3</v>
       </c>
       <c r="BG5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI5" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>9.6</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>7.8</v>
@@ -1882,46 +1882,46 @@
         <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V6" t="n">
         <v>2.56</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.16</v>
@@ -1930,7 +1930,7 @@
         <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
         <v>970</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AO6" t="n">
         <v>8.6</v>
@@ -1996,107 +1996,107 @@
         <v>4.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
       <c r="AY6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU6" t="n">
         <v>3.3</v>
       </c>
-      <c r="BH6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3</v>
-      </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.4</v>
+        <v>1.51</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>1.63</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
         <v>5.6</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -2145,7 +2145,7 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2154,7 +2154,7 @@
         <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
         <v>1.65</v>
@@ -2175,7 +2175,7 @@
         <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
         <v>2.28</v>
@@ -2238,7 +2238,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
         <v>5.1</v>
@@ -2271,7 +2271,7 @@
         <v>3.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
         <v>4.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -2384,55 +2384,55 @@
         <v>1.58</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.93</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.92</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2441,7 +2441,7 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2468,16 +2468,16 @@
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
         <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,61 +2489,61 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>3.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
         <v>2.76</v>
@@ -2552,59 +2552,59 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>2.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.94</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.94</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="I9" t="n">
         <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1.55</v>
@@ -2668,7 +2668,7 @@
         <v>1.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
@@ -2683,16 +2683,16 @@
         <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
@@ -2707,16 +2707,16 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2743,58 +2743,58 @@
         <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="n">
         <v>2.68</v>
@@ -2806,59 +2806,59 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>20</v>
+        <v>1.19</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,28 +2913,28 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
         <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.02</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>3.7</v>
@@ -3158,7 +3158,7 @@
         <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.52</v>
@@ -3308,7 +3308,7 @@
         <v>2.92</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3341,7 +3341,7 @@
         <v>1.65</v>
       </c>
       <c r="BT11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
         <v>3.55</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
         <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.29</v>
@@ -3427,7 +3427,7 @@
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
         <v>1.76</v>
@@ -3436,7 +3436,7 @@
         <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
         <v>1.9</v>
@@ -3562,7 +3562,7 @@
         <v>3.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
         <v>4.5</v>
@@ -3666,7 +3666,7 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.41</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
@@ -3953,10 +3953,10 @@
         <v>1.76</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -4076,7 +4076,7 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
         <v>3.45</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
         <v>1.49</v>
@@ -4192,10 +4192,10 @@
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
         <v>5.2</v>
@@ -4210,7 +4210,7 @@
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X15" t="n">
         <v>9.4</v>
@@ -4225,7 +4225,7 @@
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>8.4</v>
@@ -4240,7 +4240,7 @@
         <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
@@ -4252,7 +4252,7 @@
         <v>48</v>
       </c>
       <c r="AK15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
         <v>65</v>
@@ -4261,22 +4261,22 @@
         <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO15" t="n">
         <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
         <v>7.2</v>
@@ -4288,7 +4288,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -4297,28 +4297,28 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.3</v>
@@ -4443,49 +4443,49 @@
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
         <v>23</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>75</v>
@@ -4497,7 +4497,7 @@
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>75</v>
@@ -4512,13 +4512,13 @@
         <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
         <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -4533,7 +4533,7 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -4545,10 +4545,10 @@
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>13.5</v>
@@ -4563,13 +4563,13 @@
         <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
@@ -4578,7 +4578,7 @@
         <v>3.85</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="n">
         <v>3.3</v>
@@ -4691,7 +4691,7 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>1.31</v>
@@ -4718,13 +4718,13 @@
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
         <v>30</v>
@@ -4733,22 +4733,22 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>20</v>
@@ -4769,7 +4769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
         <v>46</v>
@@ -4787,7 +4787,7 @@
         <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
         <v>1.01</v>
@@ -4832,7 +4832,7 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-07 13:23:55</t>
+          <t>2026-06-07 15:32:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -881,34 +881,34 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -920,7 +920,7 @@
         <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
         <v>8.199999999999999</v>
@@ -989,13 +989,13 @@
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>18</v>
+        <v>3.95</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.5</v>
+        <v>3.9</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>13</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -1389,19 +1389,19 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
         <v>2.32</v>
@@ -1410,7 +1410,7 @@
         <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
@@ -1428,7 +1428,7 @@
         <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1467,64 +1467,64 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
         <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
@@ -1670,7 +1670,7 @@
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>55</v>
@@ -1802,7 +1802,7 @@
         <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1981,19 +1981,19 @@
         <v>8.6</v>
       </c>
       <c r="AP6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AT6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -2005,31 +2005,31 @@
         <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>2.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>2.76</v>
       </c>
       <c r="BG6" t="n">
         <v>5.7</v>
@@ -2068,19 +2068,19 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="BT6" t="n">
         <v>18.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2151,7 +2151,7 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
@@ -2175,10 +2175,10 @@
         <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2196,13 +2196,13 @@
         <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2238,13 +2238,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AT7" t="n">
         <v>5.2</v>
@@ -2253,10 +2253,10 @@
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -2265,28 +2265,28 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2298,13 +2298,13 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BN7" t="n">
         <v>4.1</v>
@@ -2316,25 +2316,25 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -2405,13 +2405,13 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
@@ -2420,16 +2420,16 @@
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
         <v>2.46</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
@@ -2489,64 +2489,64 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>3.4</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BE8" t="n">
         <v>3.65</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BN8" t="n">
         <v>4.1</v>
@@ -2570,19 +2570,19 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2594,17 +2594,17 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2635,82 +2635,82 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
         <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
         <v>970</v>
@@ -2719,19 +2719,19 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2740,125 +2740,125 @@
         <v>70</v>
       </c>
       <c r="AO9" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.24</v>
+        <v>1.34</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>1.44</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M10" t="n">
         <v>1.08</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="N10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.2</v>
       </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -3143,64 +3143,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z11" t="n">
         <v>970</v>
@@ -3215,7 +3215,7 @@
         <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
         <v>40</v>
@@ -3227,7 +3227,7 @@
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>70</v>
@@ -3236,7 +3236,7 @@
         <v>85</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL11" t="n">
         <v>85</v>
@@ -3251,61 +3251,61 @@
         <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.6</v>
       </c>
-      <c r="BF11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH11" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BI11" t="n">
         <v>2.32</v>
@@ -3320,13 +3320,13 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3344,19 +3344,19 @@
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G12" t="n">
         <v>1.52</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.59</v>
-      </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
         <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -3457,34 +3457,34 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
         <v>970</v>
@@ -3493,91 +3493,91 @@
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO12" t="n">
         <v>130</v>
       </c>
-      <c r="AN12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>110</v>
-      </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
       <c r="BB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC12" t="n">
-        <v>13</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO12" t="n">
         <v>3.2</v>
@@ -3592,25 +3592,25 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
         <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -3675,7 +3675,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>1.43</v>
@@ -3693,7 +3693,7 @@
         <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.86</v>
@@ -3702,7 +3702,7 @@
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
@@ -3711,7 +3711,7 @@
         <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
         <v>150</v>
@@ -3759,7 +3759,7 @@
         <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
         <v>12</v>
@@ -3792,7 +3792,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -3810,7 +3810,7 @@
         <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="n">
         <v>3</v>
@@ -3837,22 +3837,22 @@
         <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3926,10 +3926,10 @@
         <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O14" t="n">
         <v>1.52</v>
@@ -3938,7 +3938,7 @@
         <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
@@ -3947,10 +3947,10 @@
         <v>5.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
         <v>1.26</v>
@@ -3959,7 +3959,7 @@
         <v>1.9</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>14.5</v>
@@ -3977,7 +3977,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
         <v>100</v>
@@ -3989,7 +3989,7 @@
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>120</v>
@@ -4016,28 +4016,28 @@
         <v>3.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AY14" t="n">
         <v>3.6</v>
@@ -4064,7 +4064,7 @@
         <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="n">
         <v>2.82</v>
@@ -4076,31 +4076,31 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
         <v>8</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
@@ -4183,7 +4183,7 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
         <v>1.52</v>
@@ -4195,7 +4195,7 @@
         <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>5.2</v>
@@ -4207,10 +4207,10 @@
         <v>1.81</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
         <v>9.4</v>
@@ -4225,7 +4225,7 @@
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
         <v>8.4</v>
@@ -4237,7 +4237,7 @@
         <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
         <v>14.5</v>
@@ -4273,13 +4273,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
@@ -4288,7 +4288,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -4297,28 +4297,28 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5</v>
-      </c>
       <c r="BD15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
@@ -4348,7 +4348,7 @@
         <v>23</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.3</v>
@@ -4443,10 +4443,10 @@
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
@@ -4461,46 +4461,46 @@
         <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
         <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
         <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -4518,125 +4518,125 @@
         <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>7.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH16" t="n">
         <v>3.85</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.32</v>
+        <v>7.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.41</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
         <v>4</v>
@@ -4682,10 +4682,10 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4697,7 +4697,7 @@
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
         <v>1.9</v>
@@ -4718,7 +4718,7 @@
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -4751,7 +4751,7 @@
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>60</v>
@@ -4775,61 +4775,61 @@
         <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI17" t="n">
         <v>2.82</v>
@@ -4838,13 +4838,13 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
@@ -4856,41 +4856,41 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-07 15:32:25</t>
+          <t>2026-06-07 17:40:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,13 +866,13 @@
         <v>4.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -911,55 +911,55 @@
         <v>2.02</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>180</v>
@@ -971,22 +971,22 @@
         <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -998,7 +998,7 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -1159,22 +1159,22 @@
         <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1183,94 +1183,94 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AZ3" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>11</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="n">
         <v>4.3</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1401,10 +1401,10 @@
         <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
         <v>1.57</v>
@@ -1425,22 +1425,22 @@
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,16 +1452,16 @@
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,61 +1470,61 @@
         <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
@@ -1548,7 +1548,7 @@
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
@@ -1667,7 +1667,7 @@
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
         <v>2.14</v>
@@ -1676,16 +1676,16 @@
         <v>55</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC5" t="n">
         <v>15</v>
@@ -1694,73 +1694,73 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL5" t="n">
         <v>22</v>
       </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>24</v>
-      </c>
       <c r="AM5" t="n">
-        <v>46</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1769,16 +1769,16 @@
         <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="n">
         <v>6.2</v>
@@ -1790,7 +1790,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
@@ -1814,7 +1814,7 @@
         <v>17</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
@@ -1927,16 +1927,16 @@
         <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AB6" t="n">
         <v>950</v>
@@ -1945,55 +1945,55 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="AG6" t="n">
         <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AI6" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="AO6" t="n">
         <v>8.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -2005,31 +2005,31 @@
         <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.76</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
         <v>5.7</v>
@@ -2044,19 +2044,19 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2074,13 +2074,13 @@
         <v>18.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2151,13 +2151,13 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
         <v>2.24</v>
@@ -2175,28 +2175,28 @@
         <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
@@ -2205,7 +2205,7 @@
         <v>140</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -2217,46 +2217,46 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="AT7" t="n">
         <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -2265,28 +2265,28 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -2408,139 +2408,139 @@
         <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE8" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.65</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,91 +2626,91 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Juventud Unida San Miguel</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
         <v>970</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
         <v>970</v>
@@ -2725,147 +2725,147 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.8</v>
+        <v>2.12</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.8</v>
+        <v>2.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Trasandino</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.22</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.31</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
         <v>65</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
         <v>130</v>
       </c>
-      <c r="AN10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>50</v>
-      </c>
       <c r="AP10" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.85</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="AW10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BB10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>CD Trasandino</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC11" t="n">
         <v>3.95</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="BD11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI11" t="n">
         <v>2.64</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>1.07</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medell</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.49</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="AR12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB12" t="n">
         <v>7.8</v>
       </c>
-      <c r="J12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X12" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.6</v>
+        <v>1.64</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS13" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="AT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>2.28</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BN13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>13</v>
+        <v>1.45</v>
       </c>
       <c r="BZ13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>11</v>
+        <v>2.58</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.02</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
         <v>11</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD14" t="n">
         <v>40</v>
       </c>
-      <c r="AA14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="BZ14" t="n">
         <v>34</v>
       </c>
-      <c r="AK14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA14" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -4150,40 +4150,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
         <v>1.52</v>
@@ -4192,204 +4192,204 @@
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.77</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK16" t="n">
         <v>42</v>
       </c>
-      <c r="AA16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 17:40:41</t>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>
@@ -4658,55 +4658,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -4715,37 +4715,37 @@
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
@@ -4754,88 +4754,88 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
         <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE17" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
         <v>4.9</v>
@@ -4844,53 +4844,307 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-07 19:48:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>1.11</v>
       </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
         <v>4</v>
       </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>1.15</v>
       </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
         <v>1.08</v>
       </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
         <v>4.1</v>
       </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>1.08</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>1.12</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>1.08</v>
       </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-06-07 17:40:41</t>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-07 19:48:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
         <v>1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
@@ -887,10 +887,10 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
@@ -899,13 +899,13 @@
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
         <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>2.02</v>
@@ -926,10 +926,10 @@
         <v>7.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>480</v>
@@ -974,7 +974,7 @@
         <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>5.9</v>
@@ -986,19 +986,19 @@
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -1007,16 +1007,16 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1383,22 +1383,22 @@
         <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R4" t="n">
         <v>1.6</v>
@@ -1425,7 +1425,7 @@
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1440,7 +1440,7 @@
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,37 +1452,37 @@
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
         <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
@@ -1494,7 +1494,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1506,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1515,10 +1515,10 @@
         <v>9</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="BF4" t="n">
         <v>4.1</v>
@@ -1536,37 +1536,37 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
         <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
         <v>4.6</v>
@@ -1643,25 +1643,25 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1.32</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
@@ -1688,7 +1688,7 @@
         <v>22</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
@@ -1697,7 +1697,7 @@
         <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
@@ -1730,13 +1730,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1748,10 +1748,10 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
@@ -1760,7 +1760,7 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1775,16 +1775,16 @@
         <v>18</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="n">
         <v>6.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
@@ -1796,22 +1796,22 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN5" t="n">
         <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS5" t="n">
         <v>12.5</v>
@@ -1820,29 +1820,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CA5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
         <v>1.73</v>
@@ -2160,7 +2160,7 @@
         <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2178,7 +2178,7 @@
         <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -2202,19 +2202,19 @@
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF7" t="n">
         <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2238,25 +2238,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.98</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -2265,28 +2265,28 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.98</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.8</v>
@@ -2411,16 +2411,16 @@
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -2429,10 +2429,10 @@
         <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X8" t="n">
         <v>24</v>
@@ -2450,7 +2450,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,7 +2459,7 @@
         <v>490</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
         <v>36</v>
@@ -2531,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
         <v>6.6</v>
@@ -2570,7 +2570,7 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
         <v>9.800000000000001</v>
@@ -2752,49 +2752,49 @@
         <v>2.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="BB9" t="n">
         <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
         <v>3.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BF9" t="n">
         <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
         <v>4.2</v>
@@ -2922,19 +2922,19 @@
         <v>1.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
         <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
@@ -2943,7 +2943,7 @@
         <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -3006,7 +3006,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
         <v>5.5</v>
@@ -3015,70 +3015,70 @@
         <v>6</v>
       </c>
       <c r="AV10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AY10" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>1.43</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.44</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3087,7 +3087,7 @@
         <v>1.29</v>
       </c>
       <c r="BT10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BU10" t="n">
         <v>4.7</v>
@@ -3102,17 +3102,17 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.8</v>
@@ -3200,7 +3200,7 @@
         <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3215,7 +3215,7 @@
         <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
@@ -3236,7 +3236,7 @@
         <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3257,7 +3257,7 @@
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
         <v>4.2</v>
@@ -3269,19 +3269,19 @@
         <v>4.4</v>
       </c>
       <c r="AV11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY11" t="n">
         <v>3.6</v>
       </c>
-      <c r="AW11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BA11" t="n">
         <v>4.2</v>
@@ -3290,7 +3290,7 @@
         <v>4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
         <v>4.1</v>
@@ -3308,7 +3308,7 @@
         <v>3.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="n">
         <v>2.34</v>
       </c>
       <c r="I12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
@@ -3421,31 +3421,31 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
       </c>
       <c r="P12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.61</v>
       </c>
       <c r="W12" t="n">
         <v>1.34</v>
@@ -3463,10 +3463,10 @@
         <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
         <v>23</v>
@@ -3478,7 +3478,7 @@
         <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
         <v>60</v>
@@ -3514,19 +3514,19 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
         <v>16.5</v>
@@ -3535,28 +3535,28 @@
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG12" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>7</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H13" t="n">
         <v>6.8</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3684,34 +3684,34 @@
         <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
         <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3720,97 +3720,97 @@
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BB13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="n">
         <v>3.85</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="BN13" t="n">
         <v>4.1</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G14" t="n">
         <v>2.06</v>
@@ -3914,13 +3914,13 @@
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.5</v>
@@ -3929,7 +3929,7 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
@@ -3938,7 +3938,7 @@
         <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -3947,10 +3947,10 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V14" t="n">
         <v>1.2</v>
@@ -3959,13 +3959,13 @@
         <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,16 +3974,16 @@
         <v>7.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
         <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
@@ -4013,19 +4013,19 @@
         <v>280</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -4034,19 +4034,19 @@
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BB14" t="n">
         <v>21</v>
@@ -4058,13 +4058,13 @@
         <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BF14" t="n">
         <v>17</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="n">
         <v>3</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
         <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
@@ -4192,7 +4192,7 @@
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -4201,7 +4201,7 @@
         <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
         <v>1.76</v>
@@ -4228,7 +4228,7 @@
         <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -4267,58 +4267,58 @@
         <v>160</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="n">
         <v>2.82</v>
@@ -4342,7 +4342,7 @@
         <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4360,7 +4360,7 @@
         <v>8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
         <v>3.25</v>
@@ -4425,37 +4425,37 @@
         <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
         <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
         <v>1.79</v>
@@ -4464,7 +4464,7 @@
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4479,7 +4479,7 @@
         <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
@@ -4527,10 +4527,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,37 +4542,37 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH16" t="n">
         <v>2.76</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H17" t="n">
         <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
         <v>4.6</v>
@@ -4688,10 +4688,10 @@
         <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -4703,10 +4703,10 @@
         <v>1.79</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -4718,7 +4718,7 @@
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -4832,7 +4832,7 @@
         <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>
@@ -4936,16 +4936,16 @@
         <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>1.31</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-07 19:48:29</t>
+          <t>2026-06-07 21:56:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -884,13 +884,13 @@
         <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
@@ -899,7 +899,7 @@
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
         <v>1.76</v>
@@ -911,7 +911,7 @@
         <v>2.02</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
@@ -923,7 +923,7 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
@@ -935,7 +935,7 @@
         <v>480</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -947,10 +947,10 @@
         <v>450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
         <v>120</v>
@@ -968,13 +968,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>5.9</v>
@@ -983,10 +983,10 @@
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,10 +995,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -1007,19 +1007,19 @@
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI2" t="n">
         <v>2.66</v>
@@ -1028,13 +1028,13 @@
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.4</v>
@@ -1046,41 +1046,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1144,19 +1144,19 @@
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
         <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.41</v>
@@ -1165,10 +1165,10 @@
         <v>1.68</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1219,16 +1219,16 @@
         <v>46</v>
       </c>
       <c r="AP3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1237,40 +1237,40 @@
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>5.9</v>
       </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BD3" t="n">
         <v>6</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
         <v>4.3</v>
@@ -1279,7 +1279,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
         <v>4.6</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
         <v>1.89</v>
@@ -1374,43 +1374,43 @@
         <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
@@ -1434,7 +1434,7 @@
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1446,10 +1446,10 @@
         <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1467,25 +1467,25 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
@@ -1494,10 +1494,10 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>8.199999999999999</v>
@@ -1518,31 +1518,31 @@
         <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
         <v>5.8</v>
       </c>
       <c r="BH4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK4" t="n">
         <v>4.7</v>
       </c>
-      <c r="BI4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1560,10 +1560,10 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
         <v>4.5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
         <v>1.88</v>
@@ -1634,7 +1634,7 @@
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.17</v>
@@ -1655,7 +1655,7 @@
         <v>1.32</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S5" t="n">
         <v>1.8</v>
@@ -1664,16 +1664,16 @@
         <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
@@ -1721,7 +1721,7 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO5" t="n">
         <v>21</v>
@@ -1757,16 +1757,16 @@
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA5" t="n">
         <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
         <v>6</v>
@@ -1790,7 +1790,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>17.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
@@ -1823,7 +1823,7 @@
         <v>4.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5" t="n">
         <v>7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1873,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
@@ -1909,7 +1909,7 @@
         <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
         <v>2.76</v>
@@ -1918,10 +1918,10 @@
         <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.16</v>
@@ -1942,7 +1942,7 @@
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>36</v>
@@ -1957,7 +1957,7 @@
         <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
@@ -1981,7 +1981,7 @@
         <v>8.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.8</v>
@@ -1993,7 +1993,7 @@
         <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -2005,31 +2005,31 @@
         <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
       </c>
       <c r="BC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
         <v>5.7</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2071,7 +2071,7 @@
         <v>1.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BU6" t="n">
         <v>3.3</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
         <v>1.73</v>
@@ -2142,7 +2142,7 @@
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2157,7 +2157,7 @@
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
@@ -2172,13 +2172,13 @@
         <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
         <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -2217,7 +2217,7 @@
         <v>160</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
         <v>65</v>
@@ -2238,25 +2238,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AT7" t="n">
         <v>5.2</v>
       </c>
       <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -2265,10 +2265,10 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
@@ -2277,16 +2277,16 @@
         <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2304,13 +2304,13 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="BN7" t="n">
         <v>4.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -2411,7 +2411,7 @@
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
         <v>1.93</v>
@@ -2420,64 +2420,64 @@
         <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>490</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="AJ8" t="n">
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2486,22 +2486,22 @@
         <v>29</v>
       </c>
       <c r="AO8" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
         <v>7.8</v>
@@ -2510,19 +2510,19 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>4.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
@@ -2543,7 +2543,7 @@
         <v>4.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
         <v>2.78</v>
@@ -2558,13 +2558,13 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.19</v>
+        <v>1.99</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2576,35 +2576,35 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2668,25 +2668,25 @@
         <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
         <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,13 +2695,13 @@
         <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
@@ -2731,7 +2731,7 @@
         <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2743,122 +2743,122 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AT9" t="n">
         <v>5.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AX9" t="n">
         <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH9" t="n">
         <v>3.3</v>
       </c>
-      <c r="BE9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
         <v>4.2</v>
@@ -2910,40 +2910,40 @@
         <v>1.57</v>
       </c>
       <c r="M10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.14</v>
       </c>
       <c r="S10" t="n">
         <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2964,7 +2964,7 @@
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2991,22 +2991,22 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="AT10" t="n">
         <v>5.5</v>
@@ -3015,40 +3015,40 @@
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BH10" t="n">
         <v>2.56</v>
@@ -3060,13 +3060,13 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -3161,19 +3161,19 @@
         <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -3182,7 +3182,7 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
         <v>1.78</v>
@@ -3197,10 +3197,10 @@
         <v>1.65</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3209,34 +3209,34 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
       </c>
       <c r="AJ11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK11" t="n">
         <v>500</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>110</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3251,55 +3251,55 @@
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC11" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG11" t="n">
         <v>6.2</v>
@@ -3308,7 +3308,7 @@
         <v>3.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="n">
         <v>2.34</v>
@@ -3409,10 +3409,10 @@
         <v>2.66</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3421,7 +3421,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
@@ -3430,7 +3430,7 @@
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -3439,7 +3439,7 @@
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
         <v>1.84</v>
@@ -3448,13 +3448,13 @@
         <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
         <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z12" t="n">
         <v>26</v>
@@ -3514,19 +3514,19 @@
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
         <v>16.5</v>
@@ -3535,28 +3535,28 @@
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>8</v>
-      </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3681,7 +3681,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
         <v>1.74</v>
@@ -3696,16 +3696,16 @@
         <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
         <v>29</v>
@@ -3714,7 +3714,7 @@
         <v>65</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
@@ -3726,16 +3726,16 @@
         <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
@@ -3747,58 +3747,58 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
         <v>21</v>
       </c>
       <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD13" t="n">
         <v>26</v>
@@ -3807,10 +3807,10 @@
         <v>32</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="n">
         <v>3.85</v>
@@ -3840,7 +3840,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
         <v>2.06</v>
@@ -3914,7 +3914,7 @@
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3929,7 +3929,7 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
@@ -3944,7 +3944,7 @@
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
         <v>2.04</v>
@@ -4121,14 +4121,14 @@
         <v>13.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
         <v>11.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
         <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.47</v>
@@ -4183,37 +4183,37 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
         <v>1.92</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
@@ -4222,7 +4222,7 @@
         <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -4246,7 +4246,7 @@
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
@@ -4258,13 +4258,13 @@
         <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN15" t="n">
         <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP15" t="n">
         <v>8.4</v>
@@ -4273,10 +4273,10 @@
         <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
         <v>5.8</v>
@@ -4288,7 +4288,7 @@
         <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -4297,28 +4297,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="n">
         <v>2.82</v>
@@ -4342,7 +4342,7 @@
         <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
         <v>3.15</v>
@@ -4431,10 +4431,10 @@
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
         <v>2.7</v>
@@ -4443,28 +4443,28 @@
         <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q16" t="n">
         <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4479,7 +4479,7 @@
         <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
@@ -4509,28 +4509,28 @@
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
         <v>210</v>
       </c>
       <c r="AN16" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,58 +4542,58 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BD16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF16" t="n">
-        <v>36</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
         <v>4.1</v>
@@ -4602,13 +4602,13 @@
         <v>23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -4667,31 +4667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
         <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -4706,16 +4706,16 @@
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
         <v>2.08</v>
@@ -4733,10 +4733,10 @@
         <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4748,7 +4748,7 @@
         <v>12.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
@@ -4757,19 +4757,19 @@
         <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>65</v>
@@ -4778,13 +4778,13 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -4796,19 +4796,19 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
@@ -4817,16 +4817,16 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="n">
         <v>3.8</v>
@@ -4850,7 +4850,7 @@
         <v>4.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
         <v>13.5</v>
@@ -4868,7 +4868,7 @@
         <v>8.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -4948,7 +4948,7 @@
         <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
         <v>1.88</v>
@@ -4957,22 +4957,22 @@
         <v>1.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4996,7 +4996,7 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
         <v>970</v>
@@ -5014,7 +5014,7 @@
         <v>32</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>42</v>
@@ -5026,61 +5026,61 @@
         <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.95</v>
+        <v>2.82</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.26</v>
+        <v>3.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="BH18" t="n">
         <v>6.4</v>
@@ -5110,7 +5110,7 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
@@ -5134,7 +5134,7 @@
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-07 21:56:50</t>
+          <t>2026-06-08 00:04:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
         <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
         <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -926,7 +926,7 @@
         <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>23</v>
@@ -935,13 +935,13 @@
         <v>480</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="n">
         <v>450</v>
@@ -953,7 +953,7 @@
         <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -962,31 +962,31 @@
         <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX2" t="n">
         <v>7.6</v>
@@ -995,28 +995,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>3</v>
@@ -1025,7 +1025,7 @@
         <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
         <v>6</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>4.4</v>
@@ -1046,41 +1046,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
         <v>3.4</v>
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1138,22 +1138,22 @@
         <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
         <v>2.42</v>
@@ -1162,13 +1162,13 @@
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X3" t="n">
         <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1180,10 +1180,10 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
@@ -1192,7 +1192,7 @@
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
@@ -1204,73 +1204,73 @@
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
         <v>7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.3</v>
@@ -1279,10 +1279,10 @@
         <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,7 +1291,7 @@
         <v>8.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO3" t="n">
         <v>4.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.6</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1431,7 +1431,7 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
@@ -1443,13 +1443,13 @@
         <v>500</v>
       </c>
       <c r="AF4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="n">
         <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1461,28 +1461,28 @@
         <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1494,7 +1494,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1506,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1515,19 +1515,19 @@
         <v>9</v>
       </c>
       <c r="BD4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF4" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
         <v>3.55</v>
@@ -1536,59 +1536,59 @@
         <v>9.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.6</v>
@@ -1637,7 +1637,7 @@
         <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
@@ -1646,19 +1646,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="T5" t="n">
         <v>1.4</v>
@@ -1670,7 +1670,7 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>240</v>
@@ -1772,7 +1772,7 @@
         <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>4.6</v>
@@ -1790,7 +1790,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>17.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
@@ -1838,11 +1838,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -1873,82 +1873,82 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
         <v>350</v>
@@ -1978,10 +1978,10 @@
         <v>440</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.8</v>
@@ -2005,98 +2005,98 @@
         <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BE6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="BT6" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2127,55 +2127,55 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
         <v>2.36</v>
@@ -2193,28 +2193,28 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ7" t="n">
         <v>970</v>
@@ -2226,7 +2226,7 @@
         <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN7" t="n">
         <v>55</v>
@@ -2235,122 +2235,122 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AW7" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="BN7" t="n">
         <v>4.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.8</v>
+        <v>2.26</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.9</v>
+        <v>2.26</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
         <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
@@ -2414,19 +2414,19 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
@@ -2435,7 +2435,7 @@
         <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
         <v>17.5</v>
@@ -2459,7 +2459,7 @@
         <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>18</v>
@@ -2492,13 +2492,13 @@
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>6.2</v>
@@ -2510,10 +2510,10 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AY8" t="n">
         <v>8.199999999999999</v>
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
@@ -2543,7 +2543,7 @@
         <v>4.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
         <v>2.78</v>
@@ -2552,19 +2552,19 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>2.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="BN8" t="n">
         <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2576,10 +2576,10 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU8" t="n">
         <v>5.7</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.83</v>
+        <v>4.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
         <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,7 +2695,7 @@
         <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2704,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2725,7 +2725,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
         <v>22</v>
@@ -2737,7 +2737,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2749,10 +2749,10 @@
         <v>5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
         <v>5.3</v>
@@ -2761,40 +2761,40 @@
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
@@ -2803,62 +2803,62 @@
         <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BT9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -2889,61 +2889,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.76</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.15</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2991,128 +2991,128 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.95</v>
+        <v>1.48</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>1.47</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.8</v>
+        <v>1.62</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.7</v>
+        <v>1.63</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>1.61</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.35</v>
+        <v>1.64</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.5</v>
+        <v>1.63</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.3</v>
+        <v>1.63</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.55</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -3146,61 +3146,61 @@
         <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
         <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3209,25 +3209,25 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3251,94 +3251,94 @@
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.5</v>
+        <v>1.87</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>1.87</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.6</v>
+        <v>1.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>2.02</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.3</v>
+        <v>1.76</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.7</v>
+        <v>1.89</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>1.92</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.2</v>
+        <v>1.88</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.5</v>
+        <v>1.99</v>
       </c>
       <c r="BG11" t="n">
         <v>6.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -3400,58 +3400,58 @@
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>8.4</v>
@@ -3490,13 +3490,13 @@
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>500</v>
@@ -3526,7 +3526,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
         <v>16.5</v>
@@ -3535,10 +3535,10 @@
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
         <v>8.800000000000001</v>
@@ -3547,19 +3547,19 @@
         <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI12" t="n">
         <v>2.32</v>
@@ -3574,31 +3574,31 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU12" t="n">
         <v>4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3610,17 +3610,17 @@
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.52</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.53</v>
       </c>
       <c r="H13" t="n">
         <v>7.6</v>
@@ -3666,46 +3666,46 @@
         <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
         <v>29</v>
@@ -3714,28 +3714,28 @@
         <v>65</v>
       </c>
       <c r="AA13" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>17.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
@@ -3750,37 +3750,37 @@
         <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
         <v>8.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS13" t="n">
         <v>8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX13" t="n">
         <v>6.8</v>
@@ -3789,7 +3789,7 @@
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
         <v>7.6</v>
@@ -3801,7 +3801,7 @@
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
         <v>32</v>
@@ -3810,71 +3810,71 @@
         <v>5.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="n">
         <v>3.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.64</v>
+        <v>2.82</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -3950,7 +3950,7 @@
         <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V14" t="n">
         <v>1.2</v>
@@ -3959,10 +3959,10 @@
         <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
         <v>55</v>
@@ -4007,7 +4007,7 @@
         <v>450</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>280</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.06</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.08</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
@@ -4171,49 +4171,49 @@
         <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
         <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
@@ -4225,7 +4225,7 @@
         <v>160</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
@@ -4237,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
@@ -4252,7 +4252,7 @@
         <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
         <v>70</v>
@@ -4267,16 +4267,16 @@
         <v>170</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ15" t="n">
         <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
         <v>5.8</v>
@@ -4288,7 +4288,7 @@
         <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -4297,40 +4297,40 @@
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
         <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="n">
         <v>2.82</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4345,7 +4345,7 @@
         <v>3.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>7</v>
@@ -4360,13 +4360,13 @@
         <v>8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G16" t="n">
         <v>2.62</v>
@@ -4425,10 +4425,10 @@
         <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>1.57</v>
@@ -4437,16 +4437,16 @@
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O16" t="n">
         <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.19</v>
@@ -4455,7 +4455,7 @@
         <v>5.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
         <v>1.78</v>
@@ -4482,7 +4482,7 @@
         <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>17</v>
@@ -4491,7 +4491,7 @@
         <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
         <v>14.5</v>
@@ -4509,7 +4509,7 @@
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
         <v>210</v>
@@ -4521,16 +4521,16 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,40 +4542,40 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI16" t="n">
         <v>2.36</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN16" t="n">
         <v>5.2</v>
@@ -4608,7 +4608,7 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
         <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -4733,25 +4733,25 @@
         <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
         <v>12.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
         <v>65</v>
@@ -4763,28 +4763,28 @@
         <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -4796,19 +4796,19 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
@@ -4817,37 +4817,37 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO17" t="n">
         <v>4</v>
@@ -4856,41 +4856,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA17" t="n">
         <v>7</v>
       </c>
-      <c r="BT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4981,7 +4981,7 @@
         <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -5005,10 +5005,10 @@
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>32</v>
@@ -5029,64 +5029,64 @@
         <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
         <v>3.65</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BC18" t="n">
         <v>3.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BF18" t="n">
         <v>3.05</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BH18" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5098,53 +5098,53 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-08 00:04:25</t>
+          <t>2026-06-08 02:12:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -860,16 +860,16 @@
         <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
@@ -881,28 +881,28 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -911,10 +911,10 @@
         <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>120</v>
@@ -929,10 +929,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -962,7 +962,7 @@
         <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP2" t="n">
         <v>9</v>
@@ -971,10 +971,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT2" t="n">
         <v>6</v>
@@ -983,13 +983,13 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW2" t="n">
         <v>9.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
@@ -1016,7 +1016,7 @@
         <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -1144,7 +1144,7 @@
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
@@ -1153,7 +1153,7 @@
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
         <v>2.42</v>
@@ -1162,7 +1162,7 @@
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
         <v>48</v>
@@ -1171,7 +1171,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1183,7 +1183,7 @@
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
@@ -1219,61 +1219,61 @@
         <v>970</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
         <v>8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI3" t="n">
         <v>3.2</v>
@@ -1282,13 +1282,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>5.7</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1380,46 +1380,46 @@
         <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
         <v>2.14</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1431,13 +1431,13 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
@@ -1449,85 +1449,85 @@
         <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL4" t="n">
         <v>500</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB4" t="n">
         <v>11</v>
       </c>
-      <c r="AY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE4" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>7.2</v>
       </c>
-      <c r="BG4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
         <v>3.55</v>
@@ -1536,13 +1536,13 @@
         <v>9.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>5</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
         <v>3.95</v>
@@ -1643,16 +1643,16 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
         <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R5" t="n">
         <v>2.02</v>
@@ -1661,25 +1661,25 @@
         <v>1.84</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="Y5" t="n">
         <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1700,10 +1700,10 @@
         <v>19.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1718,7 +1718,7 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
         <v>5.6</v>
@@ -1727,58 +1727,58 @@
         <v>21</v>
       </c>
       <c r="AP5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
         <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BH5" t="n">
         <v>6.2</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
         <v>5.8</v>
@@ -1808,7 +1808,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
         <v>17.5</v>
@@ -1817,13 +1817,13 @@
         <v>12.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU5" t="n">
         <v>4.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
         <v>7</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>1.53</v>
@@ -1885,55 +1885,55 @@
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
         <v>36</v>
@@ -1951,7 +1951,7 @@
         <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="n">
         <v>950</v>
@@ -1963,25 +1963,25 @@
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK6" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="AL6" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>440</v>
+        <v>130</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.8</v>
@@ -1990,31 +1990,31 @@
         <v>5.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW6" t="n">
         <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2026,77 +2026,77 @@
         <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="BF6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>3.5</v>
       </c>
-      <c r="BH6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="BT6" t="n">
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2133,46 +2133,46 @@
         <v>1.72</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
         <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>1.16</v>
@@ -2181,7 +2181,7 @@
         <v>2.36</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC7" t="n">
         <v>15</v>
@@ -2205,7 +2205,7 @@
         <v>140</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>9.800000000000001</v>
@@ -2214,7 +2214,7 @@
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
         <v>970</v>
@@ -2226,7 +2226,7 @@
         <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AN7" t="n">
         <v>55</v>
@@ -2241,22 +2241,22 @@
         <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="AX7" t="n">
         <v>7.8</v>
@@ -2268,25 +2268,25 @@
         <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="BH7" t="n">
         <v>3.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
         <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.41</v>
@@ -2405,37 +2405,37 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2447,10 +2447,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2483,22 +2483,22 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
         <v>6.2</v>
@@ -2507,10 +2507,10 @@
         <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
         <v>7.2</v>
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2531,10 +2531,10 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
@@ -2543,68 +2543,68 @@
         <v>4.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BN8" t="n">
         <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BT8" t="n">
         <v>11.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>4.1</v>
       </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O9" t="n">
         <v>1.4</v>
@@ -2668,10 +2668,10 @@
         <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
@@ -2686,13 +2686,13 @@
         <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
         <v>70</v>
@@ -2704,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2713,7 +2713,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2725,34 +2725,34 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
         <v>5.3</v>
@@ -2761,10 +2761,10 @@
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
         <v>6.8</v>
@@ -2773,55 +2773,55 @@
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH9" t="n">
         <v>3.25</v>
       </c>
-      <c r="BB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BI9" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
         <v>13.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.9</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.72</v>
       </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.76</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
         <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
         <v>42</v>
@@ -2967,13 +2967,13 @@
         <v>270</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>390</v>
@@ -2982,10 +2982,10 @@
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AL10" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
         <v>2.6</v>
@@ -3164,31 +3164,31 @@
         <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.37</v>
@@ -3197,10 +3197,10 @@
         <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -3209,25 +3209,25 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3251,55 +3251,55 @@
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.87</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.87</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.95</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.76</v>
+        <v>4.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.89</v>
+        <v>5.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.91</v>
+        <v>5.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.88</v>
+        <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="BC11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.99</v>
+        <v>3.65</v>
       </c>
       <c r="BG11" t="n">
         <v>6.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
         <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="J12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.05</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y12" t="n">
         <v>8.4</v>
@@ -3460,19 +3460,19 @@
         <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF12" t="n">
         <v>500</v>
@@ -3481,7 +3481,7 @@
         <v>500</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
@@ -3490,7 +3490,7 @@
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3502,7 +3502,7 @@
         <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
         <v>7.2</v>
@@ -3511,55 +3511,55 @@
         <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AX12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BD12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE12" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI12" t="n">
         <v>2.32</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="BT12" t="n">
         <v>5.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
         <v>1.52</v>
@@ -3660,7 +3660,7 @@
         <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>4.6</v>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
@@ -3690,13 +3690,13 @@
         <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
@@ -3708,13 +3708,13 @@
         <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
@@ -3726,7 +3726,7 @@
         <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AF13" t="n">
         <v>11</v>
@@ -3753,10 +3753,10 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
@@ -3765,13 +3765,13 @@
         <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT13" t="n">
         <v>8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>8.4</v>
@@ -3780,7 +3780,7 @@
         <v>24</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
         <v>6.8</v>
@@ -3792,16 +3792,16 @@
         <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BE13" t="n">
         <v>32</v>
@@ -3810,10 +3810,10 @@
         <v>5.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI13" t="n">
         <v>3.1</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.5</v>
@@ -3929,16 +3929,16 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -3956,16 +3956,16 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3977,16 +3977,16 @@
         <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -3995,10 +3995,10 @@
         <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
         <v>110</v>
@@ -4007,13 +4007,13 @@
         <v>450</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>280</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
@@ -4028,16 +4028,16 @@
         <v>6.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
@@ -4049,7 +4049,7 @@
         <v>42</v>
       </c>
       <c r="BB14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
         <v>21</v>
@@ -4058,19 +4058,19 @@
         <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
         <v>38</v>
       </c>
       <c r="BH14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4097,7 +4097,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14" t="n">
         <v>11.5</v>
@@ -4106,7 +4106,7 @@
         <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -4162,25 +4162,25 @@
         <v>2.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
         <v>2.74</v>
@@ -4192,7 +4192,7 @@
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
@@ -4204,121 +4204,121 @@
         <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF15" t="n">
         <v>11</v>
       </c>
-      <c r="Y15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13</v>
-      </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BH15" t="n">
         <v>2.82</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -4425,13 +4425,13 @@
         <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
         <v>1.12</v>
@@ -4452,16 +4452,16 @@
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
         <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
         <v>1.61</v>
@@ -4488,7 +4488,7 @@
         <v>17</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>16.5</v>
@@ -4521,7 +4521,7 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.199999999999999</v>
@@ -4569,7 +4569,7 @@
         <v>5.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
         <v>5.6</v>
@@ -4596,7 +4596,7 @@
         <v>5.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
         <v>23</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -4691,22 +4691,22 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -4715,49 +4715,49 @@
         <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
         <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
         <v>970</v>
@@ -4766,85 +4766,85 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
         <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AW17" t="n">
         <v>7.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
         <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>6.6</v>
       </c>
       <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG17" t="n">
         <v>7.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN17" t="n">
         <v>4.8</v>
@@ -4853,19 +4853,19 @@
         <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17" t="n">
         <v>4.6</v>
@@ -4874,23 +4874,23 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.75</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4981,7 +4981,7 @@
         <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -5014,10 +5014,10 @@
         <v>32</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -5026,125 +5026,125 @@
         <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="BH18" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="BT18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-08 02:12:04</t>
+          <t>2026-06-08 04:19:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -875,212 +875,212 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>55</v>
       </c>
       <c r="AE2" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>450</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
         <v>19</v>
       </c>
-      <c r="AO2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
         <v>3.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
         <v>2.38</v>
@@ -1120,55 +1120,55 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.65</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1177,34 +1177,34 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
         <v>75</v>
@@ -1213,43 +1213,43 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
         <v>16.5</v>
@@ -1264,40 +1264,40 @@
         <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.2</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1431,82 +1431,82 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1515,80 +1515,80 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>5</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="U5" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
         <v>120</v>
@@ -1682,167 +1682,167 @@
         <v>110</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="AB5" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BT5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -1873,55 +1873,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1930,151 +1930,151 @@
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
         <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
         <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
         <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AK6" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AL6" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH6" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4</v>
-      </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="BT6" t="n">
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2166,13 +2166,13 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
         <v>1.16</v>
@@ -2190,34 +2190,34 @@
         <v>150</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB7" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="n">
         <v>65</v>
@@ -2226,131 +2226,131 @@
         <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN7" t="n">
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO7" t="n">
         <v>3.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.26</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -2402,10 +2402,10 @@
         <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
@@ -2414,19 +2414,19 @@
         <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
@@ -2435,7 +2435,7 @@
         <v>2.78</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2447,10 +2447,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,10 +2459,10 @@
         <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8" t="n">
         <v>950</v>
@@ -2471,22 +2471,22 @@
         <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AP8" t="n">
         <v>7</v>
@@ -2495,34 +2495,34 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2531,80 +2531,80 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
         <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>4.4</v>
       </c>
       <c r="BT8" t="n">
         <v>11.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2635,55 +2635,55 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
         <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
         <v>2.46</v>
@@ -2692,118 +2692,118 @@
         <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK9" t="n">
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AU9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI9" t="n">
         <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
         <v>5.1</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
         <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
         <v>970</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2967,13 +2967,13 @@
         <v>270</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>390</v>
@@ -2985,7 +2985,7 @@
         <v>220</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2997,122 +2997,122 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.22</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.33</v>
+        <v>3.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.33</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>3.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.33</v>
+        <v>3.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>1.35</v>
@@ -3176,13 +3176,13 @@
         <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
         <v>1.79</v>
@@ -3245,13 +3245,13 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
@@ -3260,7 +3260,7 @@
         <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>4.8</v>
@@ -3269,13 +3269,13 @@
         <v>4.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
         <v>6.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AY11" t="n">
         <v>5.2</v>
@@ -3284,7 +3284,7 @@
         <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
         <v>3.15</v>
@@ -3293,7 +3293,7 @@
         <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="BE11" t="n">
         <v>3.2</v>
@@ -3332,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
         <v>1.56</v>
@@ -3421,55 +3421,55 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
         <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AA12" t="n">
         <v>130</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE12" t="n">
         <v>90</v>
@@ -3478,7 +3478,7 @@
         <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AH12" t="n">
         <v>55</v>
@@ -3490,7 +3490,7 @@
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,128 +3499,128 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW12" t="n">
         <v>7.4</v>
       </c>
-      <c r="BH12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
         <v>4.6</v>
@@ -3669,37 +3669,37 @@
         <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R13" t="n">
         <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
         <v>2.92</v>
@@ -3708,28 +3708,28 @@
         <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z13" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13" t="n">
         <v>17.5</v>
@@ -3738,22 +3738,22 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK13" t="n">
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
         <v>130</v>
@@ -3768,19 +3768,19 @@
         <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX13" t="n">
         <v>6.8</v>
@@ -3792,7 +3792,7 @@
         <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
@@ -3801,43 +3801,43 @@
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
         <v>5.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>7.2</v>
+        <v>2.42</v>
       </c>
       <c r="BN13" t="n">
         <v>4.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.7</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -3908,64 +3908,64 @@
         <v>1.93</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
         <v>1.87</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,13 +3974,13 @@
         <v>7.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="n">
         <v>10.5</v>
@@ -3992,37 +3992,37 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="AP14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT14" t="n">
         <v>6.8</v>
@@ -4031,22 +4031,22 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW14" t="n">
         <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
         <v>20</v>
@@ -4058,77 +4058,77 @@
         <v>40</v>
       </c>
       <c r="BE14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>46</v>
       </c>
-      <c r="BF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>38</v>
-      </c>
       <c r="BH14" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT14" t="n">
         <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -4162,22 +4162,22 @@
         <v>2.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
         <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
@@ -4186,10 +4186,10 @@
         <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
         <v>2.68</v>
@@ -4204,31 +4204,31 @@
         <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
         <v>21</v>
@@ -4243,16 +4243,16 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
         <v>60</v>
@@ -4267,16 +4267,16 @@
         <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
         <v>28</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
         <v>6</v>
@@ -4285,10 +4285,10 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
         <v>9.6</v>
@@ -4297,92 +4297,92 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
         <v>22</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BE15" t="n">
         <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
         <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT15" t="n">
         <v>8</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -4422,10 +4422,10 @@
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.3</v>
@@ -4437,40 +4437,40 @@
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.72</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
         <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z16" t="n">
         <v>25</v>
@@ -4479,16 +4479,16 @@
         <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC16" t="n">
         <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
         <v>16.5</v>
@@ -4497,28 +4497,28 @@
         <v>14.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ16" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="n">
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="n">
         <v>7.8</v>
@@ -4527,22 +4527,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -4551,49 +4551,49 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB16" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB16" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.6</v>
       </c>
       <c r="BH16" t="n">
         <v>2.72</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO16" t="n">
         <v>4.2</v>
@@ -4602,41 +4602,41 @@
         <v>23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>12</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
@@ -4700,7 +4700,7 @@
         <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
         <v>1.45</v>
@@ -4709,19 +4709,19 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
@@ -4730,13 +4730,13 @@
         <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4751,7 +4751,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
         <v>65</v>
@@ -4766,131 +4766,131 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO17" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>14</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
         <v>10</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO17" t="n">
         <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>1.44</v>
@@ -4948,31 +4948,31 @@
         <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
         <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4981,13 +4981,13 @@
         <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
         <v>970</v>
@@ -5014,10 +5014,10 @@
         <v>32</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -5026,125 +5026,125 @@
         <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="AT18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5</v>
-      </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.18</v>
+        <v>2.26</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.23</v>
+        <v>6.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-08 04:19:32</t>
+          <t>2026-06-08 06:27:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,61 +857,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
         <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
         <v>2.14</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
         <v>16</v>
@@ -923,13 +923,13 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="n">
         <v>480</v>
@@ -938,13 +938,13 @@
         <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
@@ -953,52 +953,52 @@
         <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
         <v>210</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
         <v>17</v>
@@ -1010,16 +1010,16 @@
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI2" t="n">
         <v>2.44</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>4.3</v>
@@ -1049,38 +1049,38 @@
         <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
         <v>2.38</v>
@@ -1135,25 +1135,25 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
         <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
         <v>2.74</v>
@@ -1165,10 +1165,10 @@
         <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1189,13 +1189,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
         <v>85</v>
@@ -1204,7 +1204,7 @@
         <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>75</v>
@@ -1213,16 +1213,16 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>11.5</v>
@@ -1246,7 +1246,7 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
@@ -1264,31 +1264,31 @@
         <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
@@ -1300,41 +1300,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
         <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1437,16 +1437,16 @@
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>130</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>970</v>
@@ -1467,34 +1467,34 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1503,10 +1503,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1518,77 +1518,77 @@
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN4" t="n">
         <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
         <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>6.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU5" t="n">
         <v>3.8</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>6.8</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>1.52</v>
+        <v>5.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.58</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR6" t="n">
         <v>5.3</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>8</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="AX6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY6" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>3.85</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
-        <v>34</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>2.28</v>
       </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AA7" t="n">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM7" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8</v>
-      </c>
       <c r="BT7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
         <v>7.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.54</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>170</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>1.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.6</v>
+        <v>1.26</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>1.27</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>1.28</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>1.28</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>1.26</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>1.26</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>1.28</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -2635,43 +2635,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
         <v>4.2</v>
@@ -2680,40 +2680,40 @@
         <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2722,97 +2722,97 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE9" t="n">
-        <v>6</v>
-      </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
@@ -2824,48 +2824,48 @@
         <v>12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,96 +2875,96 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>CD Trasandino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2973,153 +2973,153 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
         <v>3.85</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.2</v>
       </c>
       <c r="BB10" t="n">
         <v>3.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BF10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH10" t="n">
         <v>3.3</v>
       </c>
-      <c r="BG10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BI10" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.93</v>
+        <v>1.19</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.99</v>
+        <v>1.24</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.87</v>
+        <v>1.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,108 +3129,108 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Trasandino</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>3.8</v>
       </c>
       <c r="G11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.6</v>
       </c>
-      <c r="H11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.02</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG11" t="n">
         <v>500</v>
       </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -3251,129 +3251,129 @@
         <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.15</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT11" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>1.51</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>2.94</v>
       </c>
       <c r="X12" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medell</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB13" t="n">
         <v>7.6</v>
       </c>
-      <c r="I13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
         <v>23</v>
       </c>
-      <c r="AR13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.42</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.5</v>
+        <v>11</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.26</v>
       </c>
-      <c r="S14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.19</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF14" t="n">
         <v>11</v>
       </c>
-      <c r="Y14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
         <v>140</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>23</v>
       </c>
-      <c r="AS14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>20</v>
-      </c>
       <c r="BA14" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BE14" t="n">
-        <v>70</v>
+        <v>4.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>46</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="BI14" t="n">
         <v>2.52</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13.5</v>
+        <v>2.26</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>10</v>
+        <v>2.16</v>
       </c>
       <c r="BT14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>11</v>
+        <v>2.18</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
         <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P15" t="n">
         <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>9.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>11</v>
-      </c>
       <c r="AR15" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP15" t="n">
         <v>23</v>
       </c>
-      <c r="BA15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>18</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BT15" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.72</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>5.7</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.6</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BT16" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>
@@ -4658,97 +4658,97 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.36</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
@@ -4757,394 +4757,140 @@
         <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
         <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>1.26</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.4</v>
+        <v>1.74</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="BZ17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.4</v>
+        <v>1.22</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-08 06:27:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Curico Unido</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-06-08 06:27:16</t>
+          <t>2026-06-08 08:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,67 +857,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -926,19 +926,19 @@
         <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
@@ -947,88 +947,88 @@
         <v>700</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF2" t="n">
         <v>12</v>
       </c>
-      <c r="AR2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>15</v>
-      </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,34 +1037,34 @@
         <v>12</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT2" t="n">
         <v>10</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>1.28</v>
@@ -1135,19 +1135,19 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
         <v>2.38</v>
@@ -1156,13 +1156,13 @@
         <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X3" t="n">
         <v>90</v>
@@ -1171,7 +1171,7 @@
         <v>60</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1180,7 +1180,7 @@
         <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>19.5</v>
@@ -1192,7 +1192,7 @@
         <v>30</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>14</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>46</v>
@@ -1222,7 +1222,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>11.5</v>
@@ -1243,7 +1243,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
@@ -1267,10 +1267,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1294,7 +1294,7 @@
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
@@ -1312,7 +1312,7 @@
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,40 +1389,40 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
         <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
         <v>170</v>
@@ -1434,7 +1434,7 @@
         <v>19</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1449,40 +1449,40 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1518,52 +1518,52 @@
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
         <v>7.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>5</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU4" t="n">
         <v>4.9</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>1.99</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="V5" t="n">
-        <v>2.74</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
       </c>
       <c r="Y5" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH5" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL5" t="n">
         <v>24</v>
       </c>
-      <c r="AB5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
         <v>15</v>
       </c>
-      <c r="AE5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BZ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CA5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.17</v>
+        <v>2.66</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG6" t="n">
         <v>950</v>
       </c>
-      <c r="AE6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>36</v>
-      </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AL6" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AM6" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>240</v>
+        <v>7.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.85</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BG6" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.28</v>
+        <v>5.9</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -2118,187 +2118,187 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.5</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>10</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>13</v>
       </c>
-      <c r="BA7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,28 +2307,28 @@
         <v>12</v>
       </c>
       <c r="BN7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2346,18 +2346,18 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.22</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>2.58</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="n">
-        <v>390</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.26</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
         <v>1.66</v>
@@ -2647,28 +2647,28 @@
         <v>9.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2677,10 +2677,10 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V9" t="n">
         <v>1.12</v>
@@ -2701,10 +2701,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2713,7 +2713,7 @@
         <v>200</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2728,16 +2728,16 @@
         <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2746,7 +2746,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
         <v>6</v>
@@ -2755,13 +2755,13 @@
         <v>6.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW9" t="n">
         <v>6.4</v>
@@ -2773,25 +2773,25 @@
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
         <v>6.4</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,93 +2875,93 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Trasandino</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2988,138 +2988,138 @@
         <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AQ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.75</v>
+        <v>1.28</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>1.28</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,108 +3129,108 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>CD Trasandino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI11" t="n">
         <v>500</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>290</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -3251,129 +3251,129 @@
         <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>1.23</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="BR11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>1.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>1.24</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medell</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.5</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="P12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="BR12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AO12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.3</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.81</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7</v>
       </c>
-      <c r="AU13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="BG13" t="n">
         <v>16</v>
       </c>
-      <c r="BG13" t="n">
-        <v>50</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>2.98</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
         <v>8</v>
       </c>
-      <c r="BU13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>10</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,189 +3891,189 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>32</v>
       </c>
       <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="n">
         <v>130</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AP14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG14" t="n">
         <v>60</v>
       </c>
-      <c r="AM14" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH14" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BI14" t="n">
         <v>2.52</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
         <v>6.6</v>
@@ -4082,28 +4082,28 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.26</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.16</v>
+        <v>11.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU14" t="n">
         <v>5.3</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.25</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
         <v>1.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
         <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF15" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ15" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
         <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AX15" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BF15" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="BJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
         <v>11</v>
       </c>
-      <c r="BK15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN15" t="n">
+      <c r="BT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BO15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BV15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="G16" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.74</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
       </c>
       <c r="AF16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="AZ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>13</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="BT16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>14</v>
       </c>
-      <c r="AW16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 08:36:03</t>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>
@@ -4658,239 +4658,493 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.95</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
       </c>
       <c r="AI17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
         <v>65</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ18" t="n">
         <v>30</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK18" t="n">
         <v>26</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL18" t="n">
         <v>44</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AM18" t="n">
         <v>120</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN18" t="n">
         <v>970</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO18" t="n">
         <v>55</v>
       </c>
-      <c r="AP17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AP18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC18" t="n">
         <v>21</v>
       </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="BD18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>24</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-06-08 08:36:03</t>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:44:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -857,85 +857,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="G2" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="T2" t="n">
         <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
@@ -944,97 +944,97 @@
         <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BN2" t="n">
         <v>4.1</v>
@@ -1046,41 +1046,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
         <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G3" t="n">
         <v>2.38</v>
@@ -1120,52 +1120,52 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.58</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.64</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
         <v>1.72</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
         <v>60</v>
@@ -1174,13 +1174,13 @@
         <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
         <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>19.5</v>
@@ -1195,13 +1195,13 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="n">
         <v>40</v>
@@ -1213,16 +1213,16 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>11.5</v>
@@ -1234,7 +1234,7 @@
         <v>8.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
         <v>7.8</v>
@@ -1243,13 +1243,13 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA3" t="n">
         <v>16.5</v>
@@ -1264,40 +1264,40 @@
         <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
         <v>10.5</v>
@@ -1312,19 +1312,19 @@
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1392,16 +1392,16 @@
         <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.46</v>
@@ -1413,13 +1413,13 @@
         <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
         <v>950</v>
@@ -1431,10 +1431,10 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1443,7 +1443,7 @@
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
@@ -1455,7 +1455,7 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1467,7 +1467,7 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1482,13 +1482,13 @@
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1506,7 +1506,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1518,77 +1518,77 @@
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>10</v>
       </c>
-      <c r="BK4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>14</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
         <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1643,7 +1643,7 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.13</v>
@@ -1652,22 +1652,22 @@
         <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R5" t="n">
         <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
         <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
         <v>2.12</v>
@@ -1676,7 +1676,7 @@
         <v>90</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Z5" t="n">
         <v>110</v>
@@ -1691,13 +1691,13 @@
         <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>85</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
@@ -1709,10 +1709,10 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1724,25 +1724,25 @@
         <v>6.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
@@ -1751,7 +1751,7 @@
         <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
@@ -1766,7 +1766,7 @@
         <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
         <v>19.5</v>
@@ -1775,7 +1775,7 @@
         <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
         <v>19</v>
@@ -1784,7 +1784,7 @@
         <v>5.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
@@ -1802,16 +1802,16 @@
         <v>5.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS5" t="n">
         <v>6.4</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
         <v>7.6</v>
@@ -1882,13 +1882,13 @@
         <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1897,43 +1897,43 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
         <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="W6" t="n">
         <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>25</v>
@@ -1945,7 +1945,7 @@
         <v>17.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
         <v>25</v>
@@ -1978,37 +1978,37 @@
         <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>10.5</v>
@@ -2017,86 +2017,86 @@
         <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>10.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BH6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU6" t="n">
         <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>8</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
         <v>1.71</v>
@@ -2136,19 +2136,19 @@
         <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>3.05</v>
@@ -2157,200 +2157,200 @@
         <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
         <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
         <v>500</v>
       </c>
-      <c r="AA7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>950</v>
-      </c>
       <c r="AE7" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>16.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
         <v>500</v>
       </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="AO7" t="n">
         <v>300</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.1</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.1</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
         <v>13</v>
       </c>
       <c r="BK7" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BN7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2405,28 +2405,28 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
         <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
         <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
         <v>1.15</v>
@@ -2435,10 +2435,10 @@
         <v>2.58</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
@@ -2447,40 +2447,40 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AE8" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>9.800000000000001</v>
@@ -2492,119 +2492,119 @@
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="n">
         <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
         <v>4.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
         <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>28</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
         <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H9" t="n">
         <v>7.2</v>
@@ -2650,7 +2650,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
@@ -2659,16 +2659,16 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
         <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2680,16 +2680,16 @@
         <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
         <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2716,7 +2716,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
@@ -2773,10 +2773,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
         <v>12</v>
@@ -2785,7 +2785,7 @@
         <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
         <v>6.4</v>
@@ -2797,7 +2797,7 @@
         <v>6.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI9" t="n">
         <v>2.58</v>
@@ -2806,13 +2806,13 @@
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
@@ -2824,41 +2824,41 @@
         <v>12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
         <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -2889,55 +2889,55 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K10" t="n">
-        <v>2.76</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="P10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="T10" t="n">
         <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
         <v>1.48</v>
@@ -3015,7 +3015,7 @@
         <v>3.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.8</v>
+        <v>1.28</v>
       </c>
       <c r="AW10" t="n">
         <v>1.29</v>
@@ -3060,59 +3060,59 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>30</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
         <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -3167,22 +3167,22 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
         <v>1.79</v>
@@ -3194,7 +3194,7 @@
         <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X11" t="n">
         <v>25</v>
@@ -3209,7 +3209,7 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>14</v>
@@ -3251,55 +3251,55 @@
         <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BA11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7</v>
-      </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="BE11" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="BG11" t="n">
         <v>6.2</v>
@@ -3314,59 +3314,59 @@
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.56</v>
@@ -3430,197 +3430,197 @@
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
         <v>8.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
         <v>7</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP12" t="n">
         <v>42</v>
       </c>
-      <c r="AP12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="BQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW12" t="n">
         <v>7</v>
       </c>
-      <c r="AR12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="CA12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -3654,202 +3654,202 @@
         <v>1.49</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H13" t="n">
         <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="Z13" t="n">
         <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>130</v>
       </c>
       <c r="AF13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>25</v>
       </c>
       <c r="AW13" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
         <v>46</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BD13" t="n">
         <v>17</v>
       </c>
       <c r="BE13" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.98</v>
+        <v>130</v>
       </c>
       <c r="BN13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
         <v>6.6</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
         <v>2.06</v>
@@ -3914,13 +3914,13 @@
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.51</v>
@@ -3932,10 +3932,10 @@
         <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
         <v>2.34</v>
@@ -3950,7 +3950,7 @@
         <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.21</v>
@@ -3959,7 +3959,7 @@
         <v>1.81</v>
       </c>
       <c r="X14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>13.5</v>
@@ -3968,7 +3968,7 @@
         <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB14" t="n">
         <v>7.6</v>
@@ -3980,7 +3980,7 @@
         <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
         <v>11.5</v>
@@ -3992,16 +3992,16 @@
         <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
         <v>24</v>
       </c>
-      <c r="AK14" t="n">
-        <v>25</v>
-      </c>
       <c r="AL14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4022,7 +4022,7 @@
         <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT14" t="n">
         <v>6.8</v>
@@ -4034,7 +4034,7 @@
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -4052,83 +4052,83 @@
         <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD14" t="n">
         <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BF14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR14" t="n">
         <v>36</v>
       </c>
       <c r="BS14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT14" t="n">
         <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>12</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
         <v>3.3</v>
@@ -4183,16 +4183,16 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -4207,19 +4207,19 @@
         <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
         <v>130</v>
@@ -4231,37 +4231,37 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AE15" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>210</v>
       </c>
       <c r="AN15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO15" t="n">
         <v>140</v>
@@ -4270,7 +4270,7 @@
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
         <v>27</v>
@@ -4285,13 +4285,13 @@
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>36</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
@@ -4300,7 +4300,7 @@
         <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB15" t="n">
         <v>22</v>
@@ -4312,16 +4312,16 @@
         <v>50</v>
       </c>
       <c r="BE15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BF15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI15" t="n">
         <v>2.52</v>
@@ -4330,13 +4330,13 @@
         <v>12</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>14.5</v>
+        <v>2.26</v>
       </c>
       <c r="BN15" t="n">
         <v>4.7</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT15" t="n">
         <v>8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.5</v>
+        <v>2.18</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G16" t="n">
         <v>2.64</v>
@@ -4422,22 +4422,22 @@
         <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
         <v>3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O16" t="n">
         <v>1.58</v>
@@ -4452,43 +4452,43 @@
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V16" t="n">
         <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X16" t="n">
         <v>8.6</v>
       </c>
       <c r="Y16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB16" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7.6</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
@@ -4503,10 +4503,10 @@
         <v>90</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL16" t="n">
         <v>75</v>
@@ -4518,22 +4518,22 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP16" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
@@ -4542,7 +4542,7 @@
         <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -4551,46 +4551,46 @@
         <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>38</v>
       </c>
       <c r="BG16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="n">
         <v>2.64</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ16" t="n">
         <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BN16" t="n">
         <v>5.2</v>
@@ -4599,16 +4599,16 @@
         <v>4.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
@@ -4620,23 +4620,23 @@
         <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -4667,103 +4667,103 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X17" t="n">
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK17" t="n">
         <v>970</v>
       </c>
-      <c r="AI17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>19</v>
-      </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -4772,67 +4772,67 @@
         <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH17" t="n">
         <v>3.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4841,56 +4841,56 @@
         <v>7.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU17" t="n">
         <v>4.6</v>
       </c>
-      <c r="BO17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4948,10 +4948,10 @@
         <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
         <v>2.1</v>
@@ -4960,31 +4960,31 @@
         <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
         <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
         <v>970</v>
@@ -5002,7 +5002,7 @@
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH18" t="n">
         <v>970</v>
@@ -5014,19 +5014,19 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>6</v>
@@ -5035,13 +5035,13 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT18" t="n">
         <v>8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -5059,10 +5059,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BB18" t="n">
         <v>24</v>
@@ -5074,49 +5074,49 @@
         <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="n">
         <v>3.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="BN18" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>2.22</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.39</v>
+        <v>1.93</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-08 10:44:40</t>
+          <t>2026-06-08 12:53:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medell</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>14.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>880</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="AG2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY2" t="n">
         <v>10</v>
       </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>60</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP3" t="n">
         <v>5.5</v>
       </c>
-      <c r="I3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AQ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA3" t="n">
         <v>30</v>
       </c>
-      <c r="AE3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>560</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>190</v>
-      </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
         <v>34</v>
       </c>
-      <c r="BD3" t="n">
-        <v>100</v>
-      </c>
       <c r="BE3" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG3" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.78</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BA4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>55</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>17</v>
-      </c>
       <c r="BH4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,752 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
         <v>6</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW5" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>990</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>46</v>
-      </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-08 19:17:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Union Espanola</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Union San Felipe</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-08 19:17:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Curico Unido</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>990</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-08 19:17:38</t>
+          <t>2026-06-08 21:25:11</t>
         </is>
       </c>
     </row>
